--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -10,9 +10,100 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>UI table</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SortOrder</t>
+  </si>
+  <si>
+    <t>UIPrefab</t>
+  </si>
+  <si>
+    <t>PauseCoveredUI</t>
+  </si>
+  <si>
+    <t>UIGroupId</t>
+  </si>
+  <si>
+    <t>EscapeClose</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Display order relative to group</t>
+  </si>
+  <si>
+    <t>UI prefab name</t>
+  </si>
+  <si>
+    <t>Hide covered UI in the same group</t>
+  </si>
+  <si>
+    <t>UI group id</t>
+  </si>
+  <si>
+    <t>Allow close by back input</t>
+  </si>
+  <si>
+    <t>6001</t>
+  </si>
+  <si>
+    <t>ART-006 field HUD</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Operations/FieldHudForm</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>6002</t>
+  </si>
+  <si>
+    <t>ART-006 base command hub</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Operations/BaseCommandHubForm</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20,24 +111,24 @@
   <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -56,8 +147,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -425,147 +516,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="15.125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="40.125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="25.5" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="19.25" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col min="2" max="2" bestFit="1" width="13.125" customWidth="1"/>
+    <col min="3" max="3" bestFit="1" width="15.125" customWidth="1"/>
+    <col min="4" max="4" bestFit="1" width="40.125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" bestFit="1" width="25.5" customWidth="1"/>
+    <col min="7" max="7" bestFit="1" width="10.5" customWidth="1"/>
+    <col min="8" max="8" bestFit="1" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>UI table</t>
-        </is>
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SortOrder</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>UIPrefab</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PauseCoveredUI</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>UIGroupId</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>EscapeClose</t>
-        </is>
+      <c r="A2" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
+      <c r="A3" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Display order relative to group</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>UI prefab name</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Hide covered UI in the same group</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>UI group id</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>Allow close by back input</t>
-        </is>
+      <c r="A4" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -575,10 +679,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -588,9 +692,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -71,22 +71,31 @@
     <t>Allow close by back input</t>
   </si>
   <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>最小启动菜单</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Startup/MainMenuForm</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>6001</t>
   </si>
   <si>
     <t>ART-006 field HUD</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Operations/FieldHudForm</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>6002</t>
@@ -516,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" bestFit="1" width="13.125" customWidth="1"/>
@@ -651,19 +660,45 @@
         <v>25</v>
       </c>
       <c r="D6" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="F6" s="0" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>28</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -10,109 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>UI table</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>SortOrder</t>
-  </si>
-  <si>
-    <t>UIPrefab</t>
-  </si>
-  <si>
-    <t>PauseCoveredUI</t>
-  </si>
-  <si>
-    <t>UIGroupId</t>
-  </si>
-  <si>
-    <t>EscapeClose</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Display order relative to group</t>
-  </si>
-  <si>
-    <t>UI prefab name</t>
-  </si>
-  <si>
-    <t>Hide covered UI in the same group</t>
-  </si>
-  <si>
-    <t>UI group id</t>
-  </si>
-  <si>
-    <t>Allow close by back input</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>最小启动菜单</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Startup/MainMenuForm</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6001</t>
-  </si>
-  <si>
-    <t>ART-006 field HUD</t>
-  </si>
-  <si>
-    <t>Operations/FieldHudForm</t>
-  </si>
-  <si>
-    <t>6002</t>
-  </si>
-  <si>
-    <t>ART-006 base command hub</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Operations/BaseCommandHubForm</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -120,24 +20,24 @@
   <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -156,8 +56,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -525,186 +425,1393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" bestFit="1" width="13.125" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="15.125" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="40.125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="25.5" customWidth="1"/>
-    <col min="7" max="7" bestFit="1" width="10.5" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="19.25" customWidth="1"/>
+    <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="40.125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="25.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="19.25" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UI table</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>8</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SortOrder</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UIPrefab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PauseCoveredUI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UIGroupId</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EscapeClose</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>11</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Display order relative to group</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UI prefab name</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Hide covered UI in the same group</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>UI group id</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Allow close by back input</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>22</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>最小启动菜单</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Startup/MainMenuForm</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>22</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>现场 HUD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hud/FieldHudForm</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>31</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>基地中枢</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Operations/BaseCommandHubForm</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>存档槽列表</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Startup/SaveSlotsForm</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>损坏存档恢复</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Startup/SaveRecoveryForm</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>游戏内系统菜单</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>System/SystemMenuForm</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6006</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>System/SettingsForm</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>退出流程</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>System/ExitFlowForm</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6008</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>机器库</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Operations/MachineLibraryForm</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>制造工坊</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Operations/WorkshopForm</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6010</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>组件库</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Operations/ComponentLibraryForm</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6011</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Operations/WarehouseForm</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>算法模板库</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Operations/AlgorithmLibraryForm</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6013</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>商店</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Operations/ShopForm</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6014</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>建筑图纸</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Operations/BuildCatalogForm</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>升级与改装</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Operations/UpgradeForm</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6016</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>组件选择器</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Operations/ComponentPickerForm</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6017</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>模板集中待绑定</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Operations/AlgorithmBindingForm</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6018</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>节点组件选择器</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Operations/NodeComponentPickerForm</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6019</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>世界对象选择器</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Operations/WorldObjectPickerForm</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6020</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>算法工作台</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Operations/AlgorithmEditorForm</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>世界放置与定位</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Operations/WorldPlacementForm</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>主线任务</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Operations/QuestForm</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>警报</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Operations/AlertForm</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>记录阅读</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Operations/RecordReaderForm</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>基础引导</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Operations/TutorialForm</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>新功能说明</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Operations/FeatureHelpForm</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6027</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>帮助</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Operations/HelpForm</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>通用规则说明</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Operations/RuleHelpForm</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>作物图鉴</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Operations/CropKnowledgeForm</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>操作确认</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Operations/OperationDialogForm</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6031</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>进度与报告</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Operations/ProgressReportForm</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>操作反馈</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Operations/OperationFeedbackForm</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -714,10 +1821,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -727,9 +1834,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -746,7 +746,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>6005</t>
@@ -784,7 +783,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>6006</t>
@@ -822,7 +820,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>6007</t>
@@ -860,7 +857,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>6008</t>
@@ -898,7 +894,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>6009</t>
@@ -936,7 +931,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>6010</t>
@@ -974,7 +968,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>6011</t>
@@ -1012,7 +1005,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>6012</t>
@@ -1050,7 +1042,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>6013</t>
@@ -1088,7 +1079,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>6014</t>
@@ -1126,7 +1116,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>6015</t>
@@ -1164,7 +1153,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>6016</t>
@@ -1202,7 +1190,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>6017</t>
@@ -1240,7 +1227,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>6018</t>
@@ -1278,7 +1264,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>6019</t>
@@ -1316,7 +1301,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>6020</t>
@@ -1354,7 +1338,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>6021</t>
@@ -1392,7 +1375,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>6022</t>
@@ -1430,7 +1412,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>6023</t>
@@ -1468,7 +1449,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>6024</t>
@@ -1506,7 +1486,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>6025</t>
@@ -1544,7 +1523,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>6026</t>
@@ -1582,7 +1560,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>6027</t>
@@ -1620,7 +1597,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>6028</t>
@@ -1658,7 +1634,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>6029</t>
@@ -1696,7 +1671,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>6030</t>
@@ -1734,7 +1708,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>6031</t>
@@ -1772,7 +1745,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>6032</t>
@@ -1806,6 +1778,191 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6033</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>现场详情</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Operations/FieldHudDetailForm</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>6034</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>常驻现场 HUD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hud/FieldHudResidentForm</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>6035</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>算法公开参数</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Operations/AlgorithmPublicParametersForm</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6036</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>基地中枢能源</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Operations/BaseCommandEnergyForm</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>6037</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>现场机器总览</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Operations/FieldHudMachineOverviewForm</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
